--- a/output/StructureDefinition-t-cabs-device-phd.xlsx
+++ b/output/StructureDefinition-t-cabs-device-phd.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-20T17:13:04+01:00</t>
+    <t>2025-11-21T13:42:11+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-device-phd.xlsx
+++ b/output/StructureDefinition-t-cabs-device-phd.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T13:42:11+01:00</t>
+    <t>2025-11-25T10:29:35+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-device-phd.xlsx
+++ b/output/StructureDefinition-t-cabs-device-phd.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T10:29:35+01:00</t>
+    <t>2025-12-09T09:55:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-t-cabs-device-phd.xlsx
+++ b/output/StructureDefinition-t-cabs-device-phd.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://t-cabs.org/StructureDefinition/t-cabs-device-phd</t>
+    <t>https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-device-phd</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-09T09:55:43+01:00</t>
+    <t>2026-02-19T13:21:58+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1662,7 +1662,7 @@
     <t>Type of measurement device</t>
   </si>
   <si>
-    <t>http://t-cabs.org/ValueSet/t-cabs-valueset-phdtyp</t>
+    <t>https://bih-cei.github.io/T-CABS/ValueSet/t-cabs-valueset-phdtyp</t>
   </si>
   <si>
     <t>Device.specialization.systemType.coding:MDCType.id</t>
@@ -2481,7 +2481,7 @@
     <t>Device.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://t-cabs.org/StructureDefinition/t-cabs-patient)
+    <t xml:space="preserve">Reference(https://bih-cei.github.io/T-CABS/StructureDefinition/t-cabs-patient)
 </t>
   </si>
   <si>
@@ -2936,7 +2936,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="50.3515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="62.671875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2951,7 +2951,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="82.29296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.015625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="53.34375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="20.8125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
